--- a/docs/image_benchmark/synthetic/results.xlsx
+++ b/docs/image_benchmark/synthetic/results.xlsx
@@ -12,9 +12,9 @@
     <sheet name="BD-Rate" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All metrics'!$A$1:$S$33</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Same-QP summary'!$A$1:$N$17</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'BD-Rate'!$A$1:$H$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All metrics'!$A$1:$U$33</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Same-QP summary'!$A$1:$P$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'BD-Rate'!$A$1:$H$11</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S33"/>
+  <dimension ref="A1:U33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -459,6 +459,8 @@
     <col width="14" customWidth="1" min="17" max="17"/>
     <col width="14" customWidth="1" min="18" max="18"/>
     <col width="17" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -557,6 +559,16 @@
           <t>psnr_hvs_m_luma</t>
         </is>
       </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>psnr_rgb</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>msssim_rgb</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -654,6 +666,16 @@
           <t>41.2852594220323</t>
         </is>
       </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>43.141123617436705</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>0.9994249117804666</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -751,6 +773,16 @@
           <t>40.259174541037375</t>
         </is>
       </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>42.23766216429506</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>0.9994335817541248</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -848,6 +880,16 @@
           <t>36.58587994420594</t>
         </is>
       </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>38.9186620122363</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>0.9982956159205943</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -945,6 +987,16 @@
           <t>35.46552132214577</t>
         </is>
       </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>37.82578563111953</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>0.9982874082158025</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1042,6 +1094,16 @@
           <t>31.713278095821668</t>
         </is>
       </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>34.222115725907315</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>0.9945375686862468</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1139,6 +1201,16 @@
           <t>30.458106660576245</t>
         </is>
       </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>32.952132123213296</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>0.9942849037376759</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1236,6 +1308,16 @@
           <t>24.694639415263914</t>
         </is>
       </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>27.260224013432563</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>0.9730201824234669</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1333,6 +1415,16 @@
           <t>24.68493053776935</t>
         </is>
       </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>27.251185792833674</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>0.9728625906553114</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1430,6 +1522,16 @@
           <t>50.19243031037608</t>
         </is>
       </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>47.57037366309191</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>0.9999422201500034</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1527,6 +1629,16 @@
           <t>50.044686158226355</t>
         </is>
       </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>47.65572785760445</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>0.9999429273241542</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1624,6 +1736,16 @@
           <t>48.44241362713187</t>
         </is>
       </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>46.62546154909251</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>0.9999062089028828</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1721,6 +1843,16 @@
           <t>48.473572197279566</t>
         </is>
       </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>46.22698514019671</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>0.9999024227156704</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1818,6 +1950,16 @@
           <t>45.894840913930146</t>
         </is>
       </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>44.2080833420851</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>0.9998126031093632</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1915,6 +2057,16 @@
           <t>45.9957810789464</t>
         </is>
       </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>43.784956533997416</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>0.9997959669148272</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2012,6 +2164,16 @@
           <t>43.03245164239085</t>
         </is>
       </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>41.093219287967216</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>0.9995498378516908</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2109,6 +2271,16 @@
           <t>42.89208738443945</t>
         </is>
       </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>41.44397265628833</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>0.9996047242436769</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2206,6 +2378,16 @@
           <t>52.130611172773726</t>
         </is>
       </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>47.90419473693484</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>0.9999391721063353</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2303,6 +2485,16 @@
           <t>52.09516759207539</t>
         </is>
       </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>47.71309702970833</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>0.999936075308011</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2400,6 +2592,16 @@
           <t>50.617838133617745</t>
         </is>
       </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>45.16657074578958</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>0.9998672795394747</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2497,6 +2699,16 @@
           <t>50.5109999881475</t>
         </is>
       </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>45.16536676105929</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>0.9998702692407629</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2594,6 +2806,16 @@
           <t>46.41227495907759</t>
         </is>
       </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>41.828767135439556</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>0.9996885556470473</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2691,6 +2913,16 @@
           <t>46.146101402461575</t>
         </is>
       </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>41.73321495752965</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>0.9996869951252072</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2788,6 +3020,16 @@
           <t>41.981870640074405</t>
         </is>
       </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>38.45866379812188</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>0.9992590555984501</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2885,6 +3127,16 @@
           <t>42.43880818235077</t>
         </is>
       </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>38.466964568080016</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>0.9992645842816241</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2982,6 +3234,16 @@
           <t>50.52110900731711</t>
         </is>
       </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>49.25962479518114</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>0.9999611754866032</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3079,6 +3341,16 @@
           <t>50.52110900731711</t>
         </is>
       </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>49.25962479518114</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>0.9999611754866032</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3176,6 +3448,16 @@
           <t>49.83564777719086</t>
         </is>
       </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>48.995101355230844</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>0.9999459282089935</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3273,6 +3555,16 @@
           <t>49.83564777719086</t>
         </is>
       </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>48.995101355230844</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>0.9999459282089935</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3370,6 +3662,16 @@
           <t>49.384782483028545</t>
         </is>
       </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>48.82001298503521</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>0.9999301913423219</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3467,6 +3769,16 @@
           <t>49.384782483028545</t>
         </is>
       </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>48.82001298503521</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>0.9999301913423219</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -3564,6 +3876,16 @@
           <t>48.66855118510452</t>
         </is>
       </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>47.660833553056456</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>0.9998963408470889</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -3661,9 +3983,19 @@
           <t>48.66855118510452</t>
         </is>
       </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>47.660833553056456</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>0.9998963408470889</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S33"/>
+  <autoFilter ref="A1:U33"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3674,7 +4006,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N17"/>
+  <dimension ref="A1:P17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3691,6 +4023,8 @@
     <col width="17" customWidth="1" min="12" max="12"/>
     <col width="20" customWidth="1" min="13" max="13"/>
     <col width="23" customWidth="1" min="14" max="14"/>
+    <col width="16" customWidth="1" min="15" max="15"/>
+    <col width="18" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3764,6 +4098,16 @@
           <t>psnr_hvs_m_luma_delta</t>
         </is>
       </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>psnr_rgb_delta</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>msssim_rgb_delta</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -3810,6 +4154,12 @@
       <c r="N2" t="n">
         <v>-1.026084880994922</v>
       </c>
+      <c r="O2" t="n">
+        <v>-0.9034614531416452</v>
+      </c>
+      <c r="P2" t="n">
+        <v>8.669973658226304e-06</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3856,6 +4206,12 @@
       <c r="N3" t="n">
         <v>-1.120358622060174</v>
       </c>
+      <c r="O3" t="n">
+        <v>-1.092876381116767</v>
+      </c>
+      <c r="P3" t="n">
+        <v>-8.207704791818315e-06</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -3902,6 +4258,12 @@
       <c r="N4" t="n">
         <v>-1.255171435245423</v>
       </c>
+      <c r="O4" t="n">
+        <v>-1.269983602694019</v>
+      </c>
+      <c r="P4" t="n">
+        <v>-0.000252664948570902</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3948,6 +4310,12 @@
       <c r="N5" t="n">
         <v>-0.00970887749456395</v>
       </c>
+      <c r="O5" t="n">
+        <v>-0.009038220598888813</v>
+      </c>
+      <c r="P5" t="n">
+        <v>-0.0001575917681554406</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3994,6 +4362,12 @@
       <c r="N6" t="n">
         <v>-0.1477441521497269</v>
       </c>
+      <c r="O6" t="n">
+        <v>0.08535419451254</v>
+      </c>
+      <c r="P6" t="n">
+        <v>7.071741507935769e-07</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -4040,6 +4414,12 @@
       <c r="N7" t="n">
         <v>0.03115857014769574</v>
       </c>
+      <c r="O7" t="n">
+        <v>-0.398476408895803</v>
+      </c>
+      <c r="P7" t="n">
+        <v>-3.786187212417857e-06</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -4086,6 +4466,12 @@
       <c r="N8" t="n">
         <v>0.1009401650162545</v>
       </c>
+      <c r="O8" t="n">
+        <v>-0.4231268080876802</v>
+      </c>
+      <c r="P8" t="n">
+        <v>-1.663619453595722e-05</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -4132,6 +4518,12 @@
       <c r="N9" t="n">
         <v>-0.1403642579514042</v>
       </c>
+      <c r="O9" t="n">
+        <v>0.350753368321115</v>
+      </c>
+      <c r="P9" t="n">
+        <v>5.488639198603096e-05</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -4178,6 +4570,12 @@
       <c r="N10" t="n">
         <v>-0.03544358069833464</v>
       </c>
+      <c r="O10" t="n">
+        <v>-0.1910977072265112</v>
+      </c>
+      <c r="P10" t="n">
+        <v>-3.096798324331296e-06</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -4224,6 +4622,12 @@
       <c r="N11" t="n">
         <v>-0.1068381454702418</v>
       </c>
+      <c r="O11" t="n">
+        <v>-0.00120398473028871</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.989701288202973e-06</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -4270,6 +4674,12 @@
       <c r="N12" t="n">
         <v>-0.2661735566160175</v>
       </c>
+      <c r="O12" t="n">
+        <v>-0.09555217790990866</v>
+      </c>
+      <c r="P12" t="n">
+        <v>-1.560521840082707e-06</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -4316,6 +4726,12 @@
       <c r="N13" t="n">
         <v>0.4569375422763642</v>
       </c>
+      <c r="O13" t="n">
+        <v>0.008300769958133003</v>
+      </c>
+      <c r="P13" t="n">
+        <v>5.528683174049753e-06</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -4362,6 +4778,12 @@
       <c r="N14" t="n">
         <v>0</v>
       </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -4408,6 +4830,12 @@
       <c r="N15" t="n">
         <v>0</v>
       </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -4454,6 +4882,12 @@
       <c r="N16" t="n">
         <v>0</v>
       </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -4500,9 +4934,15 @@
       <c r="N17" t="n">
         <v>0</v>
       </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N17"/>
+  <autoFilter ref="A1:P17"/>
   <conditionalFormatting sqref="E2:E17">
     <cfRule type="cellIs" priority="1" operator="greaterThan" dxfId="0">
       <formula>0</formula>
@@ -4583,6 +5023,22 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="O2:O17">
+    <cfRule type="cellIs" priority="21" operator="greaterThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="22" operator="lessThan" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P2:P17">
+    <cfRule type="cellIs" priority="23" operator="greaterThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="24" operator="lessThan" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4593,7 +5049,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4872,9 +5328,65 @@
         <v>-1.195237320487683</v>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>psnr_rgb</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>4</v>
+      </c>
+      <c r="C10" t="n">
+        <v>102.5696785698014</v>
+      </c>
+      <c r="D10" t="n">
+        <v>29.5665592116324</v>
+      </c>
+      <c r="E10" t="n">
+        <v>309.5613683008924</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-2.738781493568649</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-4.443810455111159</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-1.185237423681427</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>msssim_rgb</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>4</v>
+      </c>
+      <c r="C11" t="n">
+        <v>94.93928078300378</v>
+      </c>
+      <c r="D11" t="n">
+        <v>26.93979346067159</v>
+      </c>
+      <c r="E11" t="n">
+        <v>278.7067919021352</v>
+      </c>
+      <c r="F11" t="n">
+        <v>-0.0008225472136548025</v>
+      </c>
+      <c r="G11" t="n">
+        <v>-0.002097738455048945</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-0.0001111400284187389</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H9"/>
-  <conditionalFormatting sqref="C2:C9">
+  <autoFilter ref="A1:H11"/>
+  <conditionalFormatting sqref="C2:C11">
     <cfRule type="cellIs" priority="1" operator="greaterThan" dxfId="0">
       <formula>0</formula>
     </cfRule>
@@ -4882,7 +5394,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D9">
+  <conditionalFormatting sqref="D2:D11">
     <cfRule type="cellIs" priority="3" operator="greaterThan" dxfId="0">
       <formula>0</formula>
     </cfRule>
@@ -4890,7 +5402,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E9">
+  <conditionalFormatting sqref="E2:E11">
     <cfRule type="cellIs" priority="5" operator="greaterThan" dxfId="0">
       <formula>0</formula>
     </cfRule>
@@ -4898,7 +5410,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F9">
+  <conditionalFormatting sqref="F2:F11">
     <cfRule type="cellIs" priority="7" operator="greaterThan" dxfId="0">
       <formula>0</formula>
     </cfRule>
@@ -4906,7 +5418,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G9">
+  <conditionalFormatting sqref="G2:G11">
     <cfRule type="cellIs" priority="9" operator="greaterThan" dxfId="0">
       <formula>0</formula>
     </cfRule>
@@ -4914,7 +5426,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H9">
+  <conditionalFormatting sqref="H2:H11">
     <cfRule type="cellIs" priority="11" operator="greaterThan" dxfId="0">
       <formula>0</formula>
     </cfRule>

--- a/docs/image_benchmark/synthetic/results.xlsx
+++ b/docs/image_benchmark/synthetic/results.xlsx
@@ -573,7 +573,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>fine_texture_512x512</t>
+          <t>mixed_content_512x512</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -588,7 +588,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>27</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -598,89 +598,89 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>104557</t>
+          <t>2434</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>3.760781200684794</t>
+          <t>161.55135579293344</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>3.190826416015625</t>
+          <t>0.07427978515625</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>836.456</t>
+          <t>19.472</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>44.1277</t>
+          <t>53.004</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>52.701</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>72.2132</t>
+          <t>53.2947</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>0.99681</t>
+          <t>0.996425</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>49.3279</t>
+          <t>55.8183</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>95.170893</t>
+          <t>97.054242</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>0.9994445087965222</t>
+          <t>0.9996238518490195</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>0.9955003125359684</t>
+          <t>0.999594796991133</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>0.9959663970786693</t>
+          <t>0.9996498501849312</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>41.2852594220323</t>
+          <t>48.44241362713187</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>43.141123617436705</t>
+          <t>46.62546154909184</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>0.9994249117804666</t>
+          <t>0.9995112697443441</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>fine_texture_512x512</t>
+          <t>mixed_content_512x512</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>27</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -705,82 +705,82 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>107226</t>
+          <t>3162</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>3.667170275865928</t>
+          <t>124.35673624288425</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>3.27227783203125</t>
+          <t>0.09649658203125</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>857.808</t>
+          <t>25.296</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>42.9929</t>
+          <t>53.2334</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>52.5461</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>72.2132</t>
+          <t>53.7285</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>0.995894</t>
+          <t>0.996627</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>48.2523</t>
+          <t>56.031</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>95.355731</t>
+          <t>97.249295</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>0.9994530019702634</t>
+          <t>0.9996268573493301</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>0.9942508585584287</t>
+          <t>0.9995964903032013</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>0.9942866984304264</t>
+          <t>0.999653669297007</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>40.259174541037375</t>
+          <t>48.473572197279566</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>42.23766216429506</t>
+          <t>46.22698514019774</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>0.9994335817541248</t>
+          <t>0.9995086165887713</t>
         </is>
       </c>
     </row>
@@ -802,7 +802,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>37</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -812,82 +812,82 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>75884</t>
+          <t>3464</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>5.181803805808866</t>
+          <t>113.51501154734412</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2.3157958984375</t>
+          <t>0.105712890625</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>607.072</t>
+          <t>27.712</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>39.257</t>
+          <t>27.2914</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>54.1514</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>72.2132</t>
+          <t>54.0178</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>0.990562</t>
+          <t>0.81217</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>44.6377</t>
+          <t>32.7501</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>92.453059</t>
+          <t>79.401316</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>0.9983149454786546</t>
+          <t>0.9544628833393421</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>0.9861275164291188</t>
+          <t>0.7410705694010001</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>0.9872991522955098</t>
+          <t>0.7872327492070879</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>36.58587994420594</t>
+          <t>24.694639415263914</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>38.9186620122363</t>
+          <t>27.260224013432698</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>0.9982956159205943</t>
+          <t>0.954457844985904</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>37</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -919,89 +919,89 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>79563</t>
+          <t>4091</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>4.942196749745484</t>
+          <t>96.11733072598386</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2.428070068359375</t>
+          <t>0.124847412109375</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>636.504</t>
+          <t>32.728</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>38.0932</t>
+          <t>27.2834</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>54.1514</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>72.2132</t>
+          <t>54.0178</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>0.987489</t>
+          <t>0.811711</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>43.4896</t>
+          <t>32.7421</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>93.119782</t>
+          <t>79.556265</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>0.998307181281308</t>
+          <t>0.9542033222986691</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>0.9816874986348367</t>
+          <t>0.7403090928378241</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>0.9816082877400166</t>
+          <t>0.7870475612326117</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>35.46552132214577</t>
+          <t>24.68493053776935</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>37.82578563111953</t>
+          <t>27.251185792833784</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>0.9982874082158025</t>
+          <t>0.9541982631136108</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>fine_texture_512x512</t>
+          <t>mixed_content_512x512</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1016,7 +1016,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>22</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1026,89 +1026,89 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>48307</t>
+          <t>3478</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>8.139938311217836</t>
+          <t>113.05807935595169</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1.474212646484375</t>
+          <t>0.10614013671875</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>386.456</t>
+          <t>27.824</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>34.3372</t>
+          <t>56.6991</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>55.1319</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>72.2132</t>
+          <t>56.4279</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>0.970108</t>
+          <t>0.997549</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>39.7735</t>
+          <t>58.3307</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>87.582146</t>
+          <t>97.34455</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>0.9945566370648617</t>
+          <t>0.9997763474339837</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>0.9568900706073686</t>
+          <t>0.9997934747975971</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>0.9605864993869575</t>
+          <t>0.999834659932302</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>31.713278095821668</t>
+          <t>50.19243031037608</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>34.222115725907315</t>
+          <t>47.5703736630932</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>0.9945375686862468</t>
+          <t>0.999709293867095</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>fine_texture_512x512</t>
+          <t>mixed_content_512x512</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>22</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1133,82 +1133,82 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>56068</t>
+          <t>4089</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>7.013198259256617</t>
+          <t>96.16434336023478</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1.7110595703125</t>
+          <t>0.124786376953125</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>448.544</t>
+          <t>32.712</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>33.0505</t>
+          <t>56.1872</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>55.2179</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>72.2132</t>
+          <t>56.2867</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>0.958637</t>
+          <t>0.997403</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>38.4922</t>
+          <t>57.8515</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>88.533029</t>
+          <t>97.344135</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>0.994304929158127</t>
+          <t>0.999774697112042</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>0.941715395325675</t>
+          <t>0.9997823536487451</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>0.9420256598700973</t>
+          <t>0.9998179850330399</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>30.458106660576245</t>
+          <t>50.044686158226355</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>32.952132123213296</t>
+          <t>47.65572785760582</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>0.9942849037376759</t>
+          <t>0.9997088659572477</t>
         </is>
       </c>
     </row>
@@ -1230,7 +1230,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>32</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1240,82 +1240,82 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>3464</t>
+          <t>48307</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>113.51501154734412</t>
+          <t>8.139938311217836</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.105712890625</t>
+          <t>1.474212646484375</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>27.712</t>
+          <t>386.456</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>27.2914</t>
+          <t>34.3372</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>54.1514</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>54.0178</t>
+          <t>72.2132</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>0.81217</t>
+          <t>0.970108</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>32.7501</t>
+          <t>39.7735</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>79.401316</t>
+          <t>87.582146</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>0.9730448510473233</t>
+          <t>0.9921821165642453</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>0.7410705694010001</t>
+          <t>0.9568900706073686</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>0.7872327492070879</t>
+          <t>0.9605864993869576</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>24.694639415263914</t>
+          <t>31.713278095821668</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>27.260224013432563</t>
+          <t>34.22211572590743</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>0.9730201824234669</t>
+          <t>0.9921770100404097</t>
         </is>
       </c>
     </row>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>32</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1347,89 +1347,89 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>4091</t>
+          <t>56068</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>96.11733072598386</t>
+          <t>7.013198259256617</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.124847412109375</t>
+          <t>1.7110595703125</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>32.728</t>
+          <t>448.544</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>27.2834</t>
+          <t>33.0505</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>54.1514</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>54.0178</t>
+          <t>72.2132</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.811711</t>
+          <t>0.958637</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>32.7421</t>
+          <t>38.4922</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>79.556265</t>
+          <t>88.533029</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.972886685049343</t>
+          <t>0.9913352539206275</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.7403090928378241</t>
+          <t>0.941715395325675</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>0.7870475612326117</t>
+          <t>0.9420256598700973</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>24.68493053776935</t>
+          <t>30.458106660576245</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>27.251185792833674</t>
+          <t>32.95213212321333</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>0.9728625906553114</t>
+          <t>0.9913298594171889</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>mixed_content_512x512</t>
+          <t>fine_texture_512x512</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1444,7 +1444,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>27</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1454,89 +1454,89 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>3478</t>
+          <t>75884</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>113.05807935595169</t>
+          <t>5.181803805808866</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.10614013671875</t>
+          <t>2.3157958984375</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>27.824</t>
+          <t>607.072</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>56.6991</t>
+          <t>39.257</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>55.1319</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>56.4279</t>
+          <t>72.2132</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>0.997549</t>
+          <t>0.990562</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>58.3307</t>
+          <t>44.6377</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>97.34455</t>
+          <t>92.453059</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>0.9999839122599811</t>
+          <t>0.9975986703603936</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>0.9997934747975971</t>
+          <t>0.9861275164291188</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>0.9998346599323019</t>
+          <t>0.9872991522955098</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>50.19243031037608</t>
+          <t>36.58587994420594</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>47.57037366309191</t>
+          <t>38.91866201223635</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>0.9999422201500034</t>
+          <t>0.9975931241799131</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>mixed_content_512x512</t>
+          <t>fine_texture_512x512</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>27</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1561,82 +1561,82 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>4089</t>
+          <t>79563</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>96.16434336023478</t>
+          <t>4.942196749745484</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.124786376953125</t>
+          <t>2.428070068359375</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>32.712</t>
+          <t>636.504</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>56.1872</t>
+          <t>38.0932</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>55.2179</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>56.2867</t>
+          <t>72.2132</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>0.997403</t>
+          <t>0.987489</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>57.8515</t>
+          <t>43.4896</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>97.344135</t>
+          <t>93.119782</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>0.9999825243114261</t>
+          <t>0.9974627438860459</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>0.9997823536487451</t>
+          <t>0.9816874986348367</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>0.9998179850330399</t>
+          <t>0.9816082877400165</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>50.044686158226355</t>
+          <t>35.46552132214577</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>47.65572785760445</t>
+          <t>37.82578563111961</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>0.9999429273241542</t>
+          <t>0.9974571466497132</t>
         </is>
       </c>
     </row>
@@ -1658,7 +1658,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>32</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1668,82 +1668,82 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2434</t>
+          <t>1916</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>161.55135579293344</t>
+          <t>205.2275574112735</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.07427978515625</t>
+          <t>0.0584716796875</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>19.472</t>
+          <t>15.328</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>53.004</t>
+          <t>49.2906</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>52.701</t>
+          <t>49.9093</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>53.2947</t>
+          <t>50.5992</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>0.996425</t>
+          <t>0.994316</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>55.8183</t>
+          <t>53.1399</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>97.054242</t>
+          <t>96.759501</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>0.9999678395015512</t>
+          <t>0.9994427497716766</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>0.999594796991133</t>
+          <t>0.99901580014886</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>0.9996498501849311</t>
+          <t>0.9991472440701383</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>48.44241362713187</t>
+          <t>45.894840913930146</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>46.62546154909251</t>
+          <t>44.2080833420848</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>0.9999062089028828</t>
+          <t>0.9992296377071147</t>
         </is>
       </c>
     </row>
@@ -1765,7 +1765,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>32</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1775,89 +1775,89 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>3162</t>
+          <t>2626</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>124.35673624288425</t>
+          <t>149.73952779893375</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>0.09649658203125</t>
+          <t>0.08013916015625</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>25.296</t>
+          <t>21.008</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>53.2334</t>
+          <t>49.706</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>52.5461</t>
+          <t>49.4164</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>53.7285</t>
+          <t>50.4972</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>0.996627</t>
+          <t>0.9943</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>56.031</t>
+          <t>53.4058</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>97.249295</t>
+          <t>96.999372</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>0.9999689144613811</t>
+          <t>0.9994505111692358</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>0.9995964903032013</t>
+          <t>0.9990681295156766</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>0.999653669297007</t>
+          <t>0.9991175503477978</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>48.473572197279566</t>
+          <t>45.9957810789464</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>46.22698514019671</t>
+          <t>43.78495653399661</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>0.9999024227156704</t>
+          <t>0.9992158415254434</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>mixed_content_512x512</t>
+          <t>fine_texture_512x512</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1872,7 +1872,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>22</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1882,89 +1882,89 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>1916</t>
+          <t>104557</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>205.2275574112735</t>
+          <t>3.760781200684794</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.0584716796875</t>
+          <t>3.190826416015625</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>15.328</t>
+          <t>836.456</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>49.2906</t>
+          <t>44.1277</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>49.9093</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>50.5992</t>
+          <t>72.2132</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>0.994316</t>
+          <t>0.99681</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>53.1399</t>
+          <t>49.3279</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>96.759501</t>
+          <t>95.170893</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>0.9999333000508229</t>
+          <t>0.9992169034742637</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>0.99901580014886</t>
+          <t>0.9955003125359684</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>0.9991472440701383</t>
+          <t>0.9959663970786692</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>45.894840913930146</t>
+          <t>41.2852594220323</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>44.2080833420851</t>
+          <t>43.14112361743724</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>0.9998126031093632</t>
+          <t>0.9992113834093558</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>mixed_content_512x512</t>
+          <t>fine_texture_512x512</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1979,7 +1979,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>22</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1989,82 +1989,82 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2626</t>
+          <t>107226</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>149.73952779893375</t>
+          <t>3.667170275865928</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.08013916015625</t>
+          <t>3.27227783203125</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>21.008</t>
+          <t>857.808</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>49.706</t>
+          <t>42.9929</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>49.4164</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>50.4972</t>
+          <t>72.2132</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>0.9943</t>
+          <t>0.995894</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>53.4058</t>
+          <t>48.2523</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>96.999372</t>
+          <t>95.355731</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>0.9999376008089754</t>
+          <t>0.9991933759286156</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>0.9990681295156766</t>
+          <t>0.9942508585584287</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>0.9991175503477978</t>
+          <t>0.9942866984304264</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>45.9957810789464</t>
+          <t>40.259174541037375</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>43.784956533997416</t>
+          <t>42.23766216429545</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>0.9997959669148272</t>
+          <t>0.9991878591037883</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>0.9998494348099305</t>
+          <t>0.9991624420181354</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>41.093219287967216</t>
+          <t>41.09321928796731</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>0.9995498378516908</t>
+          <t>0.9986620767033306</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>0.9998428402022649</t>
+          <t>0.9991386942116061</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>0.9980046354006161</t>
+          <t>0.9980046354006162</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2273,12 +2273,12 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>41.44397265628833</t>
+          <t>41.44397265628826</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>0.9996047242436769</t>
+          <t>0.9987041509310114</t>
         </is>
       </c>
     </row>
@@ -2360,7 +2360,7 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>0.9999868243512792</t>
+          <t>0.9999186127630303</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
@@ -2380,12 +2380,12 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>47.90419473693484</t>
+          <t>47.90419473693704</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>0.9999391721063353</t>
+          <t>0.9993394880297118</t>
         </is>
       </c>
     </row>
@@ -2467,7 +2467,7 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>0.9999867828866469</t>
+          <t>0.9999170863291309</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
@@ -2487,19 +2487,19 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>47.71309702970833</t>
+          <t>47.71309702970836</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>0.999936075308011</t>
+          <t>0.9993018057229918</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>sharp_edges_512x512</t>
+          <t>smooth_gradient_512x512</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>22</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2524,89 +2524,89 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2589</t>
+          <t>498</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>151.8794901506373</t>
+          <t>789.5903614457832</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>0.079010009765625</t>
+          <t>0.01519775390625</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>20.712</t>
+          <t>3.984</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>55.9422</t>
+          <t>57.3464</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>50.7637</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>48.986</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>0.996792</t>
+          <t>0.997083</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>57.8002</t>
+          <t>57.2705</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>96.90556</t>
+          <t>92.386402</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>0.9999808853602615</t>
+          <t>0.9994974441490512</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>0.9993055523317607</t>
+          <t>0.9970312013855704</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>0.9995499681145822</t>
+          <t>0.9994167509073992</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>50.617838133617745</t>
+          <t>50.52110900731711</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>45.16657074578958</t>
+          <t>49.25962479518019</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>0.9998672795394747</t>
+          <t>0.9994952089834611</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>sharp_edges_512x512</t>
+          <t>smooth_gradient_512x512</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>22</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2631,82 +2631,82 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>3296</t>
+          <t>1211</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>119.30097087378641</t>
+          <t>324.7035507844756</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.1005859375</t>
+          <t>0.036956787109375</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>26.368</t>
+          <t>9.688</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>55.867</t>
+          <t>57.3464</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>50.6191</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>48.7943</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.996756</t>
+          <t>0.997083</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>57.585</t>
+          <t>57.2705</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>96.971875</t>
+          <t>92.386402</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.9999809771853021</t>
+          <t>0.9994974441490512</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.9992974126979621</t>
+          <t>0.9970312013855704</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>0.9995723714665331</t>
+          <t>0.9994167509073992</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>50.5109999881475</t>
+          <t>50.52110900731711</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>45.16536676105929</t>
+          <t>49.25962479518019</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>0.9998702692407629</t>
+          <t>0.9994952089834611</t>
         </is>
       </c>
     </row>
@@ -2728,7 +2728,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>27</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2738,82 +2738,82 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2099</t>
+          <t>2589</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>187.33492139113864</t>
+          <t>151.8794901506373</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.064056396484375</t>
+          <t>0.079010009765625</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>16.792</t>
+          <t>20.712</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>49.4422</t>
+          <t>55.9422</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>47.4538</t>
+          <t>50.7637</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>44.5812</t>
+          <t>48.986</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.992575</t>
+          <t>0.996792</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>52.6401</t>
+          <t>57.8002</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>96.273879</t>
+          <t>96.90556</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.9999441130328937</t>
+          <t>0.9998598625172067</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.9955525529377449</t>
+          <t>0.9993055523317607</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>0.9977002794385829</t>
+          <t>0.9995499681145822</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>46.41227495907759</t>
+          <t>50.617838133617745</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>41.828767135439556</t>
+          <t>45.16657074579304</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>0.9996885556470473</t>
+          <t>0.998385414645858</t>
         </is>
       </c>
     </row>
@@ -2835,7 +2835,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>27</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2845,82 +2845,82 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2825</t>
+          <t>3296</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>139.19150442477877</t>
+          <t>119.30097087378641</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.086212158203125</t>
+          <t>0.1005859375</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>26.368</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>49.296</t>
+          <t>55.867</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>47.6621</t>
+          <t>50.6191</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>44.3264</t>
+          <t>48.7943</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>0.992451</t>
+          <t>0.996756</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>52.5601</t>
+          <t>57.585</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>96.181913</t>
+          <t>96.971875</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>0.9999402991740804</t>
+          <t>0.9998601050340978</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>0.995501821932489</t>
+          <t>0.9992974126979621</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>0.9976344106417707</t>
+          <t>0.999572371466533</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>46.146101402461575</t>
+          <t>50.5109999881475</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>41.73321495752965</t>
+          <t>45.16536676105975</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>0.9996869951252072</t>
+          <t>0.9983492237662702</t>
         </is>
       </c>
     </row>
@@ -2942,7 +2942,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>32</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2952,82 +2952,82 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>1736</t>
+          <t>2099</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>226.50691244239633</t>
+          <t>187.33492139113864</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.052978515625</t>
+          <t>0.064056396484375</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>13.888</t>
+          <t>16.792</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>44.7545</t>
+          <t>49.4422</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>44.2225</t>
+          <t>47.4538</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>41.1003</t>
+          <t>44.5812</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.984229</t>
+          <t>0.992575</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>47.8204</t>
+          <t>52.6401</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>94.796175</t>
+          <t>96.273879</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0.9998360751907274</t>
+          <t>0.9992333039207756</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.9848045783527047</t>
+          <t>0.9955525529377449</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>0.9917673484150513</t>
+          <t>0.9977002794385829</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>41.981870640074405</t>
+          <t>46.41227495907759</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>38.45866379812188</t>
+          <t>41.828767135438056</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>0.9992590555984501</t>
+          <t>0.9958952044132626</t>
         </is>
       </c>
     </row>
@@ -3049,7 +3049,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>32</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -3059,89 +3059,89 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2392</t>
+          <t>2825</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>164.38795986622074</t>
+          <t>139.19150442477877</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.072998046875</t>
+          <t>0.086212158203125</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>19.136</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>45.2529</t>
+          <t>49.296</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>44.1045</t>
+          <t>47.6621</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>41.1326</t>
+          <t>44.3264</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.985</t>
+          <t>0.992451</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>48.1066</t>
+          <t>52.5601</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>94.847292</t>
+          <t>96.181913</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.9998435070859516</t>
+          <t>0.9992083791278844</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.9878953100647662</t>
+          <t>0.995501821932489</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>0.9935549347238248</t>
+          <t>0.9976344106417707</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>42.43880818235077</t>
+          <t>46.146101402461575</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>38.466964568080016</t>
+          <t>41.7332149575286</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>0.9992645842816241</t>
+          <t>0.9958004467184572</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>smooth_gradient_512x512</t>
+          <t>sharp_edges_512x512</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>37</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -3166,89 +3166,89 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>498</t>
+          <t>1736</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>789.5903614457832</t>
+          <t>226.50691244239633</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>0.01519775390625</t>
+          <t>0.052978515625</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>3.984</t>
+          <t>13.888</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>57.3464</t>
+          <t>44.7545</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>44.2225</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>41.1003</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>0.997083</t>
+          <t>0.984229</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>57.2705</t>
+          <t>47.8204</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>92.386402</t>
+          <t>94.796175</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>0.9999752725695663</t>
+          <t>0.996191954928038</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>0.9970312013855704</t>
+          <t>0.9848045783527047</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>0.9994167509073991</t>
+          <t>0.9917673484150514</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>50.52110900731711</t>
+          <t>41.981870640074405</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>49.25962479518114</t>
+          <t>38.45866379812114</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>0.9999611754866032</t>
+          <t>0.9884355156834156</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>smooth_gradient_512x512</t>
+          <t>sharp_edges_512x512</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3263,7 +3263,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>37</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -3273,82 +3273,82 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>1211</t>
+          <t>2392</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>324.7035507844756</t>
+          <t>164.38795986622074</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>0.036956787109375</t>
+          <t>0.072998046875</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>9.688</t>
+          <t>19.136</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>57.3464</t>
+          <t>45.2529</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>44.1045</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>41.1326</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>0.997083</t>
+          <t>0.985</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>57.2705</t>
+          <t>48.1066</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>92.386402</t>
+          <t>94.847292</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>0.9999752725695663</t>
+          <t>0.9964101618706424</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>0.9970312013855704</t>
+          <t>0.9878953100647662</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>0.9994167509073991</t>
+          <t>0.9935549347238247</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>50.52110900731711</t>
+          <t>42.43880818235077</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>49.25962479518114</t>
+          <t>38.46696456807878</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>0.9999611754866032</t>
+          <t>0.9886987857768652</t>
         </is>
       </c>
     </row>
@@ -3430,7 +3430,7 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>0.9999600630651819</t>
+          <t>0.9991466142513679</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
@@ -3440,7 +3440,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>0.9994107109126067</t>
+          <t>0.9994107109126066</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>48.995101355230844</t>
+          <t>48.99510135522991</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>0.9999459282089935</t>
+          <t>0.9991443748211819</t>
         </is>
       </c>
     </row>
@@ -3537,7 +3537,7 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>0.9999600630651819</t>
+          <t>0.9991466142513679</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
@@ -3547,7 +3547,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>0.9994107109126067</t>
+          <t>0.9994107109126066</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -3557,12 +3557,12 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>48.995101355230844</t>
+          <t>48.99510135522991</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>0.9999459282089935</t>
+          <t>0.9991443748211819</t>
         </is>
       </c>
     </row>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>0.9999459793849047</t>
+          <t>0.9989427832073645</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
@@ -3664,12 +3664,12 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>48.82001298503521</t>
+          <t>48.820012985034325</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>0.9999301913423219</t>
+          <t>0.998873572542697</t>
         </is>
       </c>
     </row>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>0.9999459793849047</t>
+          <t>0.9989427832073645</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>48.82001298503521</t>
+          <t>48.820012985034325</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>0.9999301913423219</t>
+          <t>0.998873572542697</t>
         </is>
       </c>
     </row>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.9999146780042535</t>
+          <t>0.9985639459935218</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
@@ -3878,12 +3878,12 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>47.660833553056456</t>
+          <t>47.66083355305667</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>0.9998963408470889</t>
+          <t>0.9985611084517235</t>
         </is>
       </c>
     </row>
@@ -3965,7 +3965,7 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>0.9999146780042535</t>
+          <t>0.9985639459935218</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
@@ -3985,12 +3985,12 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>47.660833553056456</t>
+          <t>47.66083355305667</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>0.9998963408470889</t>
+          <t>0.9985611084517235</t>
         </is>
       </c>
     </row>
@@ -4143,22 +4143,22 @@
         <v>0.1848379999999992</v>
       </c>
       <c r="K2" t="n">
-        <v>8.493173741186411e-06</v>
+        <v>-2.352754564816095e-05</v>
       </c>
       <c r="L2" t="n">
         <v>-0.001249453977539727</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.001679698648242911</v>
+        <v>-0.0016796986482428</v>
       </c>
       <c r="N2" t="n">
         <v>-1.026084880994922</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.9034614531416452</v>
+        <v>-0.9034614531417873</v>
       </c>
       <c r="P2" t="n">
-        <v>8.669973658226304e-06</v>
+        <v>-2.352430556751273e-05</v>
       </c>
     </row>
     <row r="3">
@@ -4195,22 +4195,22 @@
         <v>0.6667230000000046</v>
       </c>
       <c r="K3" t="n">
-        <v>-7.764197346604718e-06</v>
+        <v>-0.0001359264743476807</v>
       </c>
       <c r="L3" t="n">
         <v>-0.004440017794282047</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.005690864555493169</v>
+        <v>-0.00569086455549328</v>
       </c>
       <c r="N3" t="n">
         <v>-1.120358622060174</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.092876381116767</v>
+        <v>-1.092876381116739</v>
       </c>
       <c r="P3" t="n">
-        <v>-8.207704791818315e-06</v>
+        <v>-0.0001359775301998933</v>
       </c>
     </row>
     <row r="4">
@@ -4247,22 +4247,22 @@
         <v>0.9508830000000046</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.0002517079067347883</v>
+        <v>-0.000846862643617774</v>
       </c>
       <c r="L4" t="n">
         <v>-0.01517467528169358</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.01856083951686016</v>
+        <v>-0.01856083951686027</v>
       </c>
       <c r="N4" t="n">
         <v>-1.255171435245423</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.269983602694019</v>
+        <v>-1.269983602694097</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.000252664948570902</v>
+        <v>-0.000847150623220827</v>
       </c>
     </row>
     <row r="5">
@@ -4299,7 +4299,7 @@
         <v>0.154949000000002</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.0001581659979803529</v>
+        <v>-0.0002595610406730398</v>
       </c>
       <c r="L5" t="n">
         <v>-0.0007614765631760445</v>
@@ -4311,10 +4311,10 @@
         <v>-0.00970887749456395</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.009038220598888813</v>
+        <v>-0.009038220598913682</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.0001575917681554406</v>
+        <v>-0.0002595818722932464</v>
       </c>
     </row>
     <row r="6">
@@ -4351,22 +4351,22 @@
         <v>-0.000415000000003829</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.387948554976148e-06</v>
+        <v>-1.650321941659705e-06</v>
       </c>
       <c r="L6" t="n">
         <v>-1.11211488519336e-05</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.667489926204802e-05</v>
+        <v>-1.667489926215904e-05</v>
       </c>
       <c r="N6" t="n">
         <v>-0.1477441521497269</v>
       </c>
       <c r="O6" t="n">
-        <v>0.08535419451254</v>
+        <v>0.08535419451261816</v>
       </c>
       <c r="P6" t="n">
-        <v>7.071741507935769e-07</v>
+        <v>-4.279098472226295e-07</v>
       </c>
     </row>
     <row r="7">
@@ -4403,22 +4403,22 @@
         <v>0.1950530000000015</v>
       </c>
       <c r="K7" t="n">
-        <v>1.074959829927558e-06</v>
+        <v>3.00550031062663e-06</v>
       </c>
       <c r="L7" t="n">
         <v>1.693312068340447e-06</v>
       </c>
       <c r="M7" t="n">
-        <v>3.819112075920117e-06</v>
+        <v>3.819112075809095e-06</v>
       </c>
       <c r="N7" t="n">
         <v>0.03115857014769574</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.398476408895803</v>
+        <v>-0.3984764088940977</v>
       </c>
       <c r="P7" t="n">
-        <v>-3.786187212417857e-06</v>
+        <v>-2.653155572795995e-06</v>
       </c>
     </row>
     <row r="8">
@@ -4455,7 +4455,7 @@
         <v>0.2398709999999937</v>
       </c>
       <c r="K8" t="n">
-        <v>4.300758152497863e-06</v>
+        <v>7.761397559202798e-06</v>
       </c>
       <c r="L8" t="n">
         <v>5.232936681653921e-05</v>
@@ -4467,10 +4467,10 @@
         <v>0.1009401650162545</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.4231268080876802</v>
+        <v>-0.4231268080881847</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.663619453595722e-05</v>
+        <v>-1.379618167129948e-05</v>
       </c>
     </row>
     <row r="9">
@@ -4507,22 +4507,22 @@
         <v>0.1727550000000093</v>
       </c>
       <c r="K9" t="n">
-        <v>-6.59460766561093e-06</v>
+        <v>-2.37478065293617e-05</v>
       </c>
       <c r="L9" t="n">
         <v>-9.823890561644344e-05</v>
       </c>
       <c r="M9" t="n">
-        <v>-8.143092953649678e-05</v>
+        <v>-8.143092953638575e-05</v>
       </c>
       <c r="N9" t="n">
         <v>-0.1403642579514042</v>
       </c>
       <c r="O9" t="n">
-        <v>0.350753368321115</v>
+        <v>0.3507533683209516</v>
       </c>
       <c r="P9" t="n">
-        <v>5.488639198603096e-05</v>
+        <v>4.207422768076619e-05</v>
       </c>
     </row>
     <row r="10">
@@ -4559,7 +4559,7 @@
         <v>0.1473610000000036</v>
       </c>
       <c r="K10" t="n">
-        <v>-4.146463228327235e-08</v>
+        <v>-1.526433899390334e-06</v>
       </c>
       <c r="L10" t="n">
         <v>-3.056207761276131e-05</v>
@@ -4571,10 +4571,10 @@
         <v>-0.03544358069833464</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.1910977072265112</v>
+        <v>-0.1910977072286855</v>
       </c>
       <c r="P10" t="n">
-        <v>-3.096798324331296e-06</v>
+        <v>-3.768230672007711e-05</v>
       </c>
     </row>
     <row r="11">
@@ -4611,22 +4611,22 @@
         <v>0.06631500000000301</v>
       </c>
       <c r="K11" t="n">
-        <v>9.18250405712584e-08</v>
+        <v>2.425168911246445e-07</v>
       </c>
       <c r="L11" t="n">
         <v>-8.139633798531776e-06</v>
       </c>
       <c r="M11" t="n">
-        <v>2.240335195091703e-05</v>
+        <v>2.240335195080601e-05</v>
       </c>
       <c r="N11" t="n">
         <v>-0.1068381454702418</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.00120398473028871</v>
+        <v>-0.0012039847332872</v>
       </c>
       <c r="P11" t="n">
-        <v>2.989701288202973e-06</v>
+        <v>-3.619087958772749e-05</v>
       </c>
     </row>
     <row r="12">
@@ -4663,7 +4663,7 @@
         <v>-0.09196599999999933</v>
       </c>
       <c r="K12" t="n">
-        <v>-3.813858813206394e-06</v>
+        <v>-2.492479289117888e-05</v>
       </c>
       <c r="L12" t="n">
         <v>-5.073100525587737e-05</v>
@@ -4675,10 +4675,10 @@
         <v>-0.2661735566160175</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.09555217790990866</v>
+        <v>-0.09555217790945392</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.560521840082707e-06</v>
+        <v>-9.475769480538077e-05</v>
       </c>
     </row>
     <row r="13">
@@ -4715,22 +4715,22 @@
         <v>0.05111699999999075</v>
       </c>
       <c r="K13" t="n">
-        <v>7.431895224230267e-06</v>
+        <v>0.0002182069426043265</v>
       </c>
       <c r="L13" t="n">
         <v>0.003090731712061423</v>
       </c>
       <c r="M13" t="n">
-        <v>0.001787586308773514</v>
+        <v>0.001787586308773292</v>
       </c>
       <c r="N13" t="n">
         <v>0.4569375422763642</v>
       </c>
       <c r="O13" t="n">
-        <v>0.008300769958133003</v>
+        <v>0.008300769957642729</v>
       </c>
       <c r="P13" t="n">
-        <v>5.528683174049753e-06</v>
+        <v>0.000263270093449619</v>
       </c>
     </row>
     <row r="14">
@@ -5226,22 +5226,22 @@
         <v>4</v>
       </c>
       <c r="C6" t="n">
-        <v>94.41941159856719</v>
+        <v>89.90773128469758</v>
       </c>
       <c r="D6" t="n">
-        <v>26.9281564942913</v>
+        <v>33.34292238351089</v>
       </c>
       <c r="E6" t="n">
-        <v>276.9461530938739</v>
+        <v>255.5437018373786</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.0007297548312450818</v>
+        <v>-0.001746539523893499</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.002096729260528724</v>
+        <v>-0.003937017502395643</v>
       </c>
       <c r="H6" t="n">
-        <v>-3.848401550826386e-05</v>
+        <v>-0.0002068398623466743</v>
       </c>
     </row>
     <row r="7">
@@ -5282,22 +5282,22 @@
         <v>4</v>
       </c>
       <c r="C8" t="n">
-        <v>103.2983868014475</v>
+        <v>103.2983868011432</v>
       </c>
       <c r="D8" t="n">
-        <v>33.53043318770146</v>
+        <v>33.5304331877021</v>
       </c>
       <c r="E8" t="n">
-        <v>284.5232125986848</v>
+        <v>284.5232125974641</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.01194581435518811</v>
+        <v>-0.01194581435518818</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.03284146541925799</v>
+        <v>-0.03284146541925807</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.0005603096563695673</v>
+        <v>-0.0005603096563696744</v>
       </c>
     </row>
     <row r="9">
@@ -5338,22 +5338,22 @@
         <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>102.5696785698014</v>
+        <v>102.5696785697944</v>
       </c>
       <c r="D10" t="n">
-        <v>29.5665592116324</v>
+        <v>29.56655921163303</v>
       </c>
       <c r="E10" t="n">
-        <v>309.5613683008924</v>
+        <v>309.5613683008633</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.738781493568649</v>
+        <v>-2.738781493570056</v>
       </c>
       <c r="G10" t="n">
-        <v>-4.443810455111159</v>
+        <v>-4.443810455115165</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.185237423681427</v>
+        <v>-1.18523742368147</v>
       </c>
     </row>
     <row r="11">
@@ -5366,22 +5366,22 @@
         <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>94.93928078300378</v>
+        <v>88.6819263267752</v>
       </c>
       <c r="D11" t="n">
-        <v>26.93979346067159</v>
+        <v>33.34712764976941</v>
       </c>
       <c r="E11" t="n">
-        <v>278.7067919021352</v>
+        <v>249.7987775643501</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.0008225472136548025</v>
+        <v>-0.002725141611094949</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.002097738455048945</v>
+        <v>-0.003937291976033387</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.0001111400284187389</v>
+        <v>-0.0003324144924351033</v>
       </c>
     </row>
   </sheetData>
